--- a/outputs/batch/crimeData_batch_2025-04-20_21-30-12/batch_analysis/combined_results.xlsx
+++ b/outputs/batch/crimeData_batch_2025-04-20_21-30-12/batch_analysis/combined_results.xlsx
@@ -27524,9 +27524,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -27542,17 +27542,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>epochs</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>custom_generated_rows</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>rows_generated_at_runtime</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -27587,16 +27587,16 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+      <c r="D2" t="n">
+        <v>260402</v>
       </c>
       <c r="E2" t="n">
         <v>0.4161</v>
@@ -27617,34 +27617,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>100</v>
       </c>
-      <c r="C3" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+      <c r="D3" t="n">
+        <v>260402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5888</v>
+        <v>0.4019</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3467</v>
+        <v>0.4464</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5888</v>
+        <v>0.4019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4364</v>
+        <v>0.4172</v>
       </c>
       <c r="I3" t="n">
-        <v/>
+        <v>0.5091</v>
       </c>
     </row>
     <row r="4">
@@ -27653,28 +27653,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>100</v>
       </c>
-      <c r="C4" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+      <c r="D4" t="n">
+        <v>260402</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5861</v>
+        <v>0.5888</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3461</v>
+        <v>0.3467</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5861</v>
+        <v>0.5888</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4352</v>
+        <v>0.4364</v>
       </c>
       <c r="I4" t="n">
         <v/>
@@ -27683,34 +27683,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>100</v>
       </c>
-      <c r="C5" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+      <c r="D5" t="n">
+        <v>260402</v>
       </c>
       <c r="E5" t="n">
-        <v>0.589</v>
+        <v>0.5888</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5677</v>
+        <v>0.3467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.589</v>
+        <v>0.5888</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4378</v>
+        <v>0.4364</v>
       </c>
       <c r="I5" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -27719,28 +27719,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>100</v>
       </c>
-      <c r="C6" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+      <c r="D6" t="n">
+        <v>260402</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3467</v>
+        <v>0.3461</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4364</v>
+        <v>0.4352</v>
       </c>
       <c r="I6" t="n">
         <v/>
@@ -27749,34 +27749,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>260402</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3739</v>
+        <v>0.5698</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4478</v>
+        <v>0.4918</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3739</v>
+        <v>0.5698</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3975</v>
+        <v>0.4927</v>
       </c>
       <c r="I7" t="n">
-        <v/>
+        <v>0.6585</v>
       </c>
     </row>
     <row r="8">
@@ -27785,28 +27785,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>300</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>260402</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5888</v>
+        <v>0.589</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3467</v>
+        <v>0.5677</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5888</v>
+        <v>0.589</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4364</v>
+        <v>0.4378</v>
       </c>
       <c r="I8" t="n">
         <v/>
@@ -27815,34 +27815,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>260402</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5753</v>
+        <v>0.5807</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4954</v>
+        <v>0.4943</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5753</v>
+        <v>0.5807</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5152</v>
+        <v>0.5084</v>
       </c>
       <c r="I9" t="n">
-        <v/>
+        <v>0.5869</v>
       </c>
     </row>
     <row r="10">
@@ -27851,28 +27851,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>300</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>260402</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5591</v>
+        <v>0.5888</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4933</v>
+        <v>0.3467</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5591</v>
+        <v>0.5888</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5074</v>
+        <v>0.4364</v>
       </c>
       <c r="I10" t="n">
         <v/>
@@ -27881,19 +27881,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>260402</v>
       </c>
       <c r="E11" t="n">
         <v>0.5888</v>
@@ -27917,28 +27917,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>300</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>260402</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3963</v>
+        <v>0.3896</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4368</v>
+        <v>0.4545</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3963</v>
+        <v>0.3896</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4128</v>
+        <v>0.4078</v>
       </c>
       <c r="I12" t="n">
         <v/>
@@ -27947,34 +27947,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>260402</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5888</v>
+        <v>0.398</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3467</v>
+        <v>0.444</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5888</v>
+        <v>0.398</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4364</v>
+        <v>0.415</v>
       </c>
       <c r="I13" t="n">
-        <v/>
+        <v>0.508</v>
       </c>
     </row>
     <row r="14">
@@ -27983,28 +27983,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>300</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>260402</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5754</v>
+        <v>0.5888</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4742</v>
+        <v>0.3467</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5754</v>
+        <v>0.5888</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4827</v>
+        <v>0.4364</v>
       </c>
       <c r="I14" t="n">
         <v/>
@@ -28013,34 +28013,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>260402</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5702</v>
+        <v>0.5888</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4831</v>
+        <v>0.3467</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5702</v>
+        <v>0.5888</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4789</v>
+        <v>0.4364</v>
       </c>
       <c r="I15" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -28049,28 +28049,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>300</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>260402</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5888</v>
+        <v>0.5532</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3467</v>
+        <v>0.5202</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5888</v>
+        <v>0.5532</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4364</v>
+        <v>0.5128</v>
       </c>
       <c r="I16" t="n">
         <v/>
@@ -28079,34 +28079,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>500</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>260402</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3892</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4484</v>
+        <v>0.4742</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3892</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4085</v>
+        <v>0.4791</v>
       </c>
       <c r="I17" t="n">
-        <v/>
+        <v>0.6425999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -28115,28 +28115,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>500</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>260402</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5888</v>
+        <v>0.5305</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3467</v>
+        <v>0.5085</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5888</v>
+        <v>0.5305</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4364</v>
+        <v>0.4953</v>
       </c>
       <c r="I18" t="n">
         <v/>
@@ -28145,34 +28145,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>500</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>260402</v>
       </c>
       <c r="E19" t="n">
-        <v>0.569</v>
+        <v>0.5734</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.4804</v>
       </c>
       <c r="G19" t="n">
-        <v>0.569</v>
+        <v>0.5734</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5165</v>
+        <v>0.487</v>
       </c>
       <c r="I19" t="n">
-        <v/>
+        <v>0.5888</v>
       </c>
     </row>
     <row r="20">
@@ -28181,28 +28181,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>500</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>260402</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5535</v>
+        <v>0.5888</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5017</v>
+        <v>0.3467</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5535</v>
+        <v>0.5888</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5073</v>
+        <v>0.4364</v>
       </c>
       <c r="I20" t="n">
         <v/>
@@ -28211,19 +28211,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>500</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>260402</v>
       </c>
       <c r="E21" t="n">
         <v>0.5888</v>
@@ -28247,28 +28247,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1000</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C22" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D22" t="n">
+        <v>260402</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3896</v>
+        <v>0.3963</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4545</v>
+        <v>0.4368</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3896</v>
+        <v>0.3963</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4078</v>
+        <v>0.4128</v>
       </c>
       <c r="I22" t="n">
         <v/>
@@ -28277,31 +28277,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1000</v>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D23" t="n">
+        <v>260402</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5888</v>
+        <v>0.3913</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3467</v>
+        <v>0.4266</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5888</v>
+        <v>0.3913</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4364</v>
+        <v>0.4062</v>
       </c>
       <c r="I23" t="n">
         <v/>
@@ -28310,34 +28310,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1000</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D24" t="n">
+        <v>260402</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5532</v>
+        <v>0.388</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5202</v>
+        <v>0.4415</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5532</v>
+        <v>0.388</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5128</v>
+        <v>0.4072</v>
       </c>
       <c r="I24" t="n">
-        <v/>
+        <v>0.5095</v>
       </c>
     </row>
     <row r="25">
@@ -28346,28 +28346,28 @@
           <t>CTGAN</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1000</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D25" t="n">
+        <v>260402</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5305</v>
+        <v>0.5888</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5085</v>
+        <v>0.3467</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5305</v>
+        <v>0.5888</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4953</v>
+        <v>0.4364</v>
       </c>
       <c r="I25" t="n">
         <v/>
@@ -28376,19 +28376,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1000</v>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C26" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D26" t="n">
+        <v>260402</v>
       </c>
       <c r="E26" t="n">
         <v>0.5888</v>
@@ -28409,64 +28409,64 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D27" t="n">
+        <v>260402</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3905</v>
+        <v>0.1637</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4258</v>
+        <v>0.0268</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3905</v>
+        <v>0.1637</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4048</v>
+        <v>0.046</v>
       </c>
       <c r="I27" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>300</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D28" t="n">
+        <v>260402</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5888</v>
+        <v>0.5754</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3467</v>
+        <v>0.4742</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5888</v>
+        <v>0.5754</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4364</v>
+        <v>0.4827</v>
       </c>
       <c r="I28" t="n">
         <v/>
@@ -28478,16 +28478,16 @@
           <t>GaussianCopula</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>300</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D29" t="n">
+        <v>260402</v>
       </c>
       <c r="E29" t="n">
         <v>0.5888</v>
@@ -28508,64 +28508,64 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D30" t="n">
+        <v>260402</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5878</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4698</v>
+        <v>0.4992</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5878</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4434</v>
+        <v>0.5011</v>
       </c>
       <c r="I30" t="n">
-        <v/>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>300</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D31" t="n">
+        <v>260402</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5888</v>
+        <v>0.5702</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3467</v>
+        <v>0.4831</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5888</v>
+        <v>0.5702</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4364</v>
+        <v>0.4789</v>
       </c>
       <c r="I31" t="n">
         <v/>
@@ -28577,28 +28577,28 @@
           <t>GaussianCopula</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>300</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C32" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D32" t="n">
+        <v>260402</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3913</v>
+        <v>0.5869</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4266</v>
+        <v>0.4478</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3913</v>
+        <v>0.5869</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4062</v>
+        <v>0.441</v>
       </c>
       <c r="I32" t="n">
         <v/>
@@ -28607,52 +28607,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C33" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D33" t="n">
+        <v>260402</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5888</v>
+        <v>0.5853</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3467</v>
+        <v>0.4901</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5888</v>
+        <v>0.5853</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4364</v>
+        <v>0.5012</v>
       </c>
       <c r="I33" t="n">
-        <v/>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>300</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C34" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D34" t="n">
+        <v>260402</v>
       </c>
       <c r="E34" t="n">
         <v>0.5888</v>
@@ -28676,28 +28676,28 @@
           <t>GaussianCopula</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>300</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C35" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D35" t="n">
+        <v>260402</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5869</v>
+        <v>0.5888</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4478</v>
+        <v>0.3467</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5869</v>
+        <v>0.5888</v>
       </c>
       <c r="H35" t="n">
-        <v>0.441</v>
+        <v>0.4364</v>
       </c>
       <c r="I35" t="n">
         <v/>
@@ -28706,19 +28706,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>300</v>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C36" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D36" t="n">
+        <v>260402</v>
       </c>
       <c r="E36" t="n">
         <v>0.5888</v>
@@ -28739,34 +28739,34 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>100</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C37" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D37" t="n">
+        <v>260402</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4019</v>
+        <v>0.3892</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4464</v>
+        <v>0.4484</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4019</v>
+        <v>0.3892</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4172</v>
+        <v>0.4085</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5091</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -28775,64 +28775,64 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>100</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C38" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D38" t="n">
+        <v>260402</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5888</v>
+        <v>0.4526</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3467</v>
+        <v>0.4675</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5888</v>
+        <v>0.4526</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4364</v>
+        <v>0.4589</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>100</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C39" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D39" t="n">
+        <v>260402</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5698</v>
+        <v>0.5888</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4918</v>
+        <v>0.3467</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5698</v>
+        <v>0.5888</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4927</v>
+        <v>0.4364</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6585</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -28841,61 +28841,61 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>100</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C40" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D40" t="n">
+        <v>260402</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5807</v>
+        <v>0.5888</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4943</v>
+        <v>0.3467</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5807</v>
+        <v>0.5888</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5084</v>
+        <v>0.4364</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5869</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>100</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C41" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D41" t="n">
+        <v>260402</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5888</v>
+        <v>0.569</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3467</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5888</v>
+        <v>0.569</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4364</v>
+        <v>0.5165</v>
       </c>
       <c r="I41" t="n">
         <v/>
@@ -28907,64 +28907,64 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>300</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C42" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D42" t="n">
+        <v>260402</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4208</v>
+        <v>0.5836</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4583</v>
+        <v>0.5208</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4208</v>
+        <v>0.5836</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4352</v>
+        <v>0.4902</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5145</v>
+        <v>0.6622</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>300</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C43" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D43" t="n">
+        <v>260402</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5888</v>
+        <v>0.5535</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3467</v>
+        <v>0.5017</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5888</v>
+        <v>0.5535</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4364</v>
+        <v>0.5073</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -28973,64 +28973,64 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>300</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C44" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D44" t="n">
+        <v>260402</v>
       </c>
       <c r="E44" t="n">
-        <v>0.513</v>
+        <v>0.592</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4932</v>
+        <v>0.5063</v>
       </c>
       <c r="G44" t="n">
-        <v>0.513</v>
+        <v>0.592</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4985</v>
+        <v>0.4907</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6241</v>
+        <v>0.6067</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>300</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C45" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D45" t="n">
+        <v>260402</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5402</v>
+        <v>0.5888</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4892</v>
+        <v>0.3467</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5402</v>
+        <v>0.5888</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5074</v>
+        <v>0.4364</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5855</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -29039,16 +29039,16 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>300</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="D46" t="n">
+        <v>260402</v>
       </c>
       <c r="E46" t="n">
         <v>0.5888</v>
@@ -29069,67 +29069,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>300</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C47" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D47" t="n">
+        <v>260402</v>
       </c>
       <c r="E47" t="n">
-        <v>0.388</v>
+        <v>0.3739</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4415</v>
+        <v>0.4478</v>
       </c>
       <c r="G47" t="n">
-        <v>0.388</v>
+        <v>0.3739</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4072</v>
+        <v>0.3975</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5095</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>300</v>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C48" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D48" t="n">
+        <v>260402</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1637</v>
+        <v>0.3905</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0268</v>
+        <v>0.4258</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1637</v>
+        <v>0.3905</v>
       </c>
       <c r="H48" t="n">
-        <v>0.046</v>
+        <v>0.4048</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -29138,82 +29138,82 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>300</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
       </c>
       <c r="C49" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D49" t="n">
+        <v>260402</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.4208</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4992</v>
+        <v>0.4583</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.4208</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5011</v>
+        <v>0.4352</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6549</v>
+        <v>0.5145</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>300</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C50" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D50" t="n">
+        <v>260402</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5853</v>
+        <v>0.5888</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4901</v>
+        <v>0.3467</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5853</v>
+        <v>0.5888</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5012</v>
+        <v>0.4364</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6022999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>300</v>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C51" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D51" t="n">
+        <v>260402</v>
       </c>
       <c r="E51" t="n">
         <v>0.5888</v>
@@ -29237,97 +29237,97 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>500</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
       </c>
       <c r="C52" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D52" t="n">
+        <v>260402</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4526</v>
+        <v>0.5888</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4675</v>
+        <v>0.3467</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4526</v>
+        <v>0.5888</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4589</v>
+        <v>0.4364</v>
       </c>
       <c r="I52" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>500</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C53" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D53" t="n">
+        <v>260402</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5888</v>
+        <v>0.5753</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3467</v>
+        <v>0.4954</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5888</v>
+        <v>0.5753</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4364</v>
+        <v>0.5152</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>500</v>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C54" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D54" t="n">
+        <v>260402</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5836</v>
+        <v>0.5888</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5208</v>
+        <v>0.3467</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5836</v>
+        <v>0.5888</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4902</v>
+        <v>0.4364</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6622</v>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -29336,61 +29336,61 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>500</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="C55" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D55" t="n">
+        <v>260402</v>
       </c>
       <c r="E55" t="n">
-        <v>0.592</v>
+        <v>0.513</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5063</v>
+        <v>0.4932</v>
       </c>
       <c r="G55" t="n">
-        <v>0.592</v>
+        <v>0.513</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4907</v>
+        <v>0.4985</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6067</v>
+        <v>0.6241</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>500</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C56" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D56" t="n">
+        <v>260402</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5888</v>
+        <v>0.5591</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3467</v>
+        <v>0.4933</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5888</v>
+        <v>0.5591</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4364</v>
+        <v>0.5074</v>
       </c>
       <c r="I56" t="n">
         <v/>
@@ -29399,34 +29399,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1000</v>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C57" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D57" t="n">
+        <v>260402</v>
       </c>
       <c r="E57" t="n">
-        <v>0.398</v>
+        <v>0.5878</v>
       </c>
       <c r="F57" t="n">
-        <v>0.444</v>
+        <v>0.4698</v>
       </c>
       <c r="G57" t="n">
-        <v>0.398</v>
+        <v>0.5878</v>
       </c>
       <c r="H57" t="n">
-        <v>0.415</v>
+        <v>0.4434</v>
       </c>
       <c r="I57" t="n">
-        <v>0.508</v>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -29435,97 +29435,97 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>1000</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
       </c>
       <c r="C58" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D58" t="n">
+        <v>260402</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5888</v>
+        <v>0.5402</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3467</v>
+        <v>0.4892</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5888</v>
+        <v>0.5402</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4364</v>
+        <v>0.5074</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.5855</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1000</v>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C59" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D59" t="n">
+        <v>260402</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5888</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4742</v>
+        <v>0.3467</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5888</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4791</v>
+        <v>0.4364</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6425999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1000</v>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C60" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D60" t="n">
+        <v>260402</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5734</v>
+        <v>0.5888</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4804</v>
+        <v>0.3467</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5734</v>
+        <v>0.5888</v>
       </c>
       <c r="H60" t="n">
-        <v>0.487</v>
+        <v>0.4364</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5888</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -29534,16 +29534,16 @@
           <t>TVAE</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>1000</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
       </c>
       <c r="C61" t="n">
-        <v>974477</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="D61" t="n">
+        <v>260402</v>
       </c>
       <c r="E61" t="n">
         <v>0.5888</v>
@@ -44237,7 +44237,7 @@
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -44278,7 +44278,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>custom_generated_rows</t>
+          <t>rows_generated_at_runtime</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -44333,7 +44333,7 @@
         <v>500</v>
       </c>
       <c r="G2" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H2" t="n">
         <v>0.4526</v>
@@ -44377,7 +44377,7 @@
         <v>300</v>
       </c>
       <c r="G3" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H3" t="n">
         <v>0.4208</v>
@@ -44421,7 +44421,7 @@
         <v>300</v>
       </c>
       <c r="G4" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H4" t="n">
         <v>0.388</v>
@@ -44465,7 +44465,7 @@
         <v>500</v>
       </c>
       <c r="G5" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H5" t="n">
         <v>0.4526</v>
@@ -44509,7 +44509,7 @@
         <v>300</v>
       </c>
       <c r="G6" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H6" t="n">
         <v>0.4208</v>
@@ -44553,7 +44553,7 @@
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H7" t="n">
         <v>0.4161</v>
@@ -44597,7 +44597,7 @@
         <v>500</v>
       </c>
       <c r="G8" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H8" t="n">
         <v>0.4526</v>
@@ -44641,7 +44641,7 @@
         <v>300</v>
       </c>
       <c r="G9" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H9" t="n">
         <v>0.4208</v>
@@ -44685,7 +44685,7 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H10" t="n">
         <v>0.4161</v>
@@ -44729,7 +44729,7 @@
         <v>500</v>
       </c>
       <c r="G11" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H11" t="n">
         <v>0.4526</v>
@@ -44773,7 +44773,7 @@
         <v>300</v>
       </c>
       <c r="G12" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H12" t="n">
         <v>0.4208</v>
@@ -44817,7 +44817,7 @@
         <v>1000</v>
       </c>
       <c r="G13" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H13" t="n">
         <v>0.3896</v>
@@ -44861,7 +44861,7 @@
         <v>500</v>
       </c>
       <c r="G14" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H14" t="n">
         <v>0.4526</v>
@@ -44905,7 +44905,7 @@
         <v>300</v>
       </c>
       <c r="G15" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H15" t="n">
         <v>0.4208</v>
@@ -44949,7 +44949,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H16" t="n">
         <v>0.4161</v>
@@ -44993,7 +44993,7 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H17" t="n">
         <v>0.5888</v>
@@ -45037,7 +45037,7 @@
         <v>1000</v>
       </c>
       <c r="G18" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H18" t="n">
         <v>0.5888</v>
@@ -45081,7 +45081,7 @@
         <v>300</v>
       </c>
       <c r="G19" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H19" t="n">
         <v>0.1637</v>
@@ -45125,7 +45125,7 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H20" t="n">
         <v>0.5888</v>
@@ -45169,7 +45169,7 @@
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H21" t="n">
         <v>0.5888</v>
@@ -45213,7 +45213,7 @@
         <v>1000</v>
       </c>
       <c r="G22" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H22" t="n">
         <v>0.5888</v>
@@ -45257,7 +45257,7 @@
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H23" t="n">
         <v>0.5888</v>
@@ -45301,7 +45301,7 @@
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H24" t="n">
         <v>0.5888</v>
@@ -45345,7 +45345,7 @@
         <v>1000</v>
       </c>
       <c r="G25" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H25" t="n">
         <v>0.5888</v>
@@ -45389,7 +45389,7 @@
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H26" t="n">
         <v>0.5888</v>
@@ -45433,7 +45433,7 @@
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H27" t="n">
         <v>0.5888</v>
@@ -45477,7 +45477,7 @@
         <v>1000</v>
       </c>
       <c r="G28" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H28" t="n">
         <v>0.5888</v>
@@ -45521,7 +45521,7 @@
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H29" t="n">
         <v>0.5888</v>
@@ -45565,7 +45565,7 @@
         <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H30" t="n">
         <v>0.5888</v>
@@ -45609,7 +45609,7 @@
         <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H31" t="n">
         <v>0.5888</v>
@@ -45653,7 +45653,7 @@
         <v>500</v>
       </c>
       <c r="G32" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H32" t="n">
         <v>0.5836</v>
@@ -45697,7 +45697,7 @@
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H33" t="n">
         <v>0.5698</v>
@@ -45741,7 +45741,7 @@
         <v>300</v>
       </c>
       <c r="G34" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H34" t="n">
         <v>0.5449000000000001</v>
@@ -45785,7 +45785,7 @@
         <v>300</v>
       </c>
       <c r="G35" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H35" t="n">
         <v>0.5888</v>
@@ -45829,7 +45829,7 @@
         <v>300</v>
       </c>
       <c r="G36" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H36" t="n">
         <v>0.5888</v>
@@ -45873,7 +45873,7 @@
         <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H37" t="n">
         <v>0.5861</v>
@@ -45917,7 +45917,7 @@
         <v>500</v>
       </c>
       <c r="G38" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H38" t="n">
         <v>0.569</v>
@@ -45961,7 +45961,7 @@
         <v>300</v>
       </c>
       <c r="G39" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H39" t="n">
         <v>0.5753</v>
@@ -46005,7 +46005,7 @@
         <v>1000</v>
       </c>
       <c r="G40" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H40" t="n">
         <v>0.5532</v>
@@ -46049,7 +46049,7 @@
         <v>500</v>
       </c>
       <c r="G41" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H41" t="n">
         <v>0.569</v>
@@ -46093,7 +46093,7 @@
         <v>500</v>
       </c>
       <c r="G42" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H42" t="n">
         <v>0.5836</v>
@@ -46137,7 +46137,7 @@
         <v>1000</v>
       </c>
       <c r="G43" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H43" t="n">
         <v>0.5532</v>
@@ -46181,7 +46181,7 @@
         <v>300</v>
       </c>
       <c r="G44" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H44" t="n">
         <v>0.5888</v>
@@ -46225,7 +46225,7 @@
         <v>300</v>
       </c>
       <c r="G45" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H45" t="n">
         <v>0.5888</v>
@@ -46269,7 +46269,7 @@
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H46" t="n">
         <v>0.5861</v>
@@ -46313,7 +46313,7 @@
         <v>500</v>
       </c>
       <c r="G47" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H47" t="n">
         <v>0.592</v>
@@ -46357,7 +46357,7 @@
         <v>300</v>
       </c>
       <c r="G48" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H48" t="n">
         <v>0.5853</v>
@@ -46401,7 +46401,7 @@
         <v>1000</v>
       </c>
       <c r="G49" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H49" t="n">
         <v>0.5734</v>
@@ -46445,7 +46445,7 @@
         <v>500</v>
       </c>
       <c r="G50" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H50" t="n">
         <v>0.592</v>
@@ -46489,7 +46489,7 @@
         <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H51" t="n">
         <v>0.589</v>
@@ -46533,7 +46533,7 @@
         <v>300</v>
       </c>
       <c r="G52" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H52" t="n">
         <v>0.5878</v>
@@ -46577,7 +46577,7 @@
         <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H53" t="n">
         <v>0.5807</v>
@@ -46621,7 +46621,7 @@
         <v>300</v>
       </c>
       <c r="G54" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H54" t="n">
         <v>0.5591</v>
@@ -46665,7 +46665,7 @@
         <v>300</v>
       </c>
       <c r="G55" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H55" t="n">
         <v>0.5402</v>
@@ -46709,7 +46709,7 @@
         <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H56" t="n">
         <v>0.589</v>
@@ -46753,7 +46753,7 @@
         <v>1000</v>
       </c>
       <c r="G57" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H57" t="n">
         <v>0.5305</v>
@@ -46797,7 +46797,7 @@
         <v>500</v>
       </c>
       <c r="G58" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H58" t="n">
         <v>0.592</v>
@@ -46841,7 +46841,7 @@
         <v>500</v>
       </c>
       <c r="G59" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H59" t="n">
         <v>0.592</v>
@@ -46885,7 +46885,7 @@
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H60" t="n">
         <v>0.589</v>
@@ -46929,7 +46929,7 @@
         <v>300</v>
       </c>
       <c r="G61" t="n">
-        <v>10000</v>
+        <v>260402</v>
       </c>
       <c r="H61" t="n">
         <v>0.5878</v>
@@ -46973,7 +46973,7 @@
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H62" t="n">
         <v>0.5888</v>
@@ -47017,7 +47017,7 @@
         <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H63" t="n">
         <v>0.5888</v>
@@ -47061,7 +47061,7 @@
         <v>1000</v>
       </c>
       <c r="G64" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H64" t="n">
         <v>0.5888</v>
@@ -47105,7 +47105,7 @@
         <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H65" t="n">
         <v>0.5888</v>
@@ -47149,7 +47149,7 @@
         <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H66" t="n">
         <v>0.5888</v>
@@ -47193,7 +47193,7 @@
         <v>1000</v>
       </c>
       <c r="G67" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H67" t="n">
         <v>0.5888</v>
@@ -47237,7 +47237,7 @@
         <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H68" t="n">
         <v>0.5888</v>
@@ -47281,7 +47281,7 @@
         <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H69" t="n">
         <v>0.5888</v>
@@ -47325,7 +47325,7 @@
         <v>1000</v>
       </c>
       <c r="G70" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H70" t="n">
         <v>0.5888</v>
@@ -47369,7 +47369,7 @@
         <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H71" t="n">
         <v>0.5888</v>
@@ -47413,7 +47413,7 @@
         <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H72" t="n">
         <v>0.5888</v>
@@ -47457,7 +47457,7 @@
         <v>1000</v>
       </c>
       <c r="G73" t="n">
-        <v>974477</v>
+        <v>260402</v>
       </c>
       <c r="H73" t="n">
         <v>0.5888</v>
